--- a/features/imports/samples/timetable-cse-3a.xlsx
+++ b/features/imports/samples/timetable-cse-3a.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>R V COLLEGE OF ENGINEERING - DEPT OF CSE - III SEMESTER 'A' SECTION - TIMETABLE 2026-27 (ODD)</t>
+          <t>DEPT OF CSE - III SEMESTER 'A' SECTION - TIMETABLE 2026-27 (ODD)</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
